--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,41 +556,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aveley FC</t>
+          <t>FC Porto B</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wingate &amp; Finchley</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>Vizela</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.9</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>45</v>
-      </c>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>434</v>
+        <v>26</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>Portugal Segunda Liga +</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -598,23 +602,17 @@
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>45</v>
-      </c>
-      <c r="N2" t="n">
-        <v>29</v>
-      </c>
-      <c r="O2" t="n">
-        <v>25</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -622,58 +620,52 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="U2" t="n">
-        <v>56.7</v>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>49.1</v>
+        <v>19.2</v>
       </c>
       <c r="W2" t="n">
-        <v>24</v>
+        <v>15.4</v>
       </c>
       <c r="X2" t="n">
-        <v>27</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>55.5</v>
+        <v>69.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>38.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>434</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sporting CP B</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Lusitânia Lourosa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="F3" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -682,11 +674,11 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>296</v>
+        <v>26</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>World AFC Champions League Elite +</t>
+          <t>Portugal Segunda Liga +</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -721,68 +713,66 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>45.9</v>
+        <v>46.2</v>
       </c>
       <c r="W3" t="n">
-        <v>21.3</v>
+        <v>42.3</v>
       </c>
       <c r="X3" t="n">
-        <v>32.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>61.8</v>
+        <v>30.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.9</v>
+        <v>15.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>296</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Neftchi Fergana</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Quwa Al Jawiya</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>원정승</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>37</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>World AFC Champions League Elite +</t>
+          <t>Russia First League +</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -790,23 +780,17 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>31</v>
-      </c>
-      <c r="N4" t="n">
-        <v>32</v>
-      </c>
-      <c r="O4" t="n">
-        <v>37</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -814,81 +798,75 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>35.3</v>
-      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>44.1</v>
+        <v>30.9</v>
       </c>
       <c r="W4" t="n">
-        <v>20.5</v>
+        <v>23.4</v>
       </c>
       <c r="X4" t="n">
-        <v>35.4</v>
+        <v>45.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>59.1</v>
+        <v>50</v>
       </c>
       <c r="Z4" t="n">
-        <v>38.6</v>
+        <v>23.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>127</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>FC Sochi</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>311</v>
+        <v>39</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Argentina Liga Profesional +</t>
+          <t>Russia First League +</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -913,22 +891,22 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>42.1</v>
+        <v>25.6</v>
       </c>
       <c r="W5" t="n">
-        <v>21.9</v>
+        <v>28.2</v>
       </c>
       <c r="X5" t="n">
-        <v>36</v>
+        <v>46.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>59.8</v>
+        <v>56.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>39.9</v>
+        <v>28.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>311</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -939,31 +917,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>281</v>
+        <v>42</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -977,7 +955,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1002,48 +980,48 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>43.8</v>
+        <v>31</v>
       </c>
       <c r="W6" t="n">
-        <v>21.4</v>
+        <v>26.2</v>
       </c>
       <c r="X6" t="n">
-        <v>34.9</v>
+        <v>42.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>61.9</v>
+        <v>40.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>41.3</v>
+        <v>26.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>281</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1052,11 +1030,11 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>270</v>
+        <v>12</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Brazil Serie A +</t>
+          <t>Argentina Liga Profesional +</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1066,7 +1044,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1091,22 +1069,22 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>44.4</v>
+        <v>41.7</v>
       </c>
       <c r="W7" t="n">
-        <v>20.7</v>
+        <v>25</v>
       </c>
       <c r="X7" t="n">
-        <v>34.8</v>
+        <v>33.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>63</v>
+        <v>33.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>41.9</v>
+        <v>16.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>270</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1136,12 +1114,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>406</v>
+        <v>131</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1180,22 +1158,22 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>40.6</v>
+        <v>34.4</v>
       </c>
       <c r="W8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="X8" t="n">
-        <v>37.2</v>
+        <v>43.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>59.1</v>
+        <v>51.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.5</v>
+        <v>22.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>406</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9">
@@ -1225,12 +1203,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1269,22 +1247,22 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>42.6</v>
+        <v>31.4</v>
       </c>
       <c r="W9" t="n">
-        <v>22</v>
+        <v>28.6</v>
       </c>
       <c r="X9" t="n">
-        <v>35.4</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>60.3</v>
+        <v>40</v>
       </c>
       <c r="Z9" t="n">
-        <v>39.7</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>305</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -1314,12 +1292,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>444</v>
+        <v>168</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1358,22 +1336,22 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>39.9</v>
+        <v>32.1</v>
       </c>
       <c r="W10" t="n">
-        <v>25.2</v>
+        <v>32.1</v>
       </c>
       <c r="X10" t="n">
-        <v>34.9</v>
+        <v>35.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>58.1</v>
+        <v>50.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>27.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>444</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -1408,7 +1386,7 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>361</v>
+        <v>93</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1447,61 +1425,61 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>43.2</v>
+        <v>40.9</v>
       </c>
       <c r="W11" t="n">
-        <v>21.3</v>
+        <v>22.6</v>
       </c>
       <c r="X11" t="n">
-        <v>35.5</v>
+        <v>36.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>62.6</v>
+        <v>61.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>39.1</v>
+        <v>30.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>361</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers U21</t>
+          <t>RED Star FC 93</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reading U21</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="E12" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>284</v>
+        <v>165</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>England Premier League 2 Division One +</t>
+          <t>France Ligue 2 +</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1511,7 +1489,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1536,22 +1514,22 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>42.3</v>
+        <v>33.3</v>
       </c>
       <c r="W12" t="n">
-        <v>21.1</v>
+        <v>30.9</v>
       </c>
       <c r="X12" t="n">
-        <v>36.6</v>
+        <v>35.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>63</v>
+        <v>49.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>41.5</v>
+        <v>24.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>284</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1562,22 +1540,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nottingham Forest U21</t>
+          <t>Jong Utrecht</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Burnley U21</t>
+          <t>Jong Ajax</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="F13" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1586,11 +1564,11 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>287</v>
+        <v>32</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>England Premier League 2 Division One +</t>
+          <t>Netherlands Eerste Divisie +</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1625,61 +1603,61 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="W13" t="n">
-        <v>21.6</v>
+        <v>15.6</v>
       </c>
       <c r="X13" t="n">
-        <v>34.8</v>
+        <v>40.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>62</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>41.1</v>
+        <v>31.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>287</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>West Ham United U21</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liverpool U21</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>293</v>
+        <v>141</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>England Premier League 2 Division One +</t>
+          <t>Portugal Primeira Liga +</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1714,48 +1692,48 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>44.7</v>
+        <v>33.3</v>
       </c>
       <c r="W14" t="n">
-        <v>19.8</v>
+        <v>29.1</v>
       </c>
       <c r="X14" t="n">
-        <v>35.5</v>
+        <v>37.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>64.8</v>
+        <v>51.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>42.7</v>
+        <v>23.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>293</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RED Star FC 93</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Estrela</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E15" t="n">
         <v>3.2</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1764,11 +1742,11 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>437</v>
+        <v>153</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>France Ligue 2 +</t>
+          <t>Portugal Primeira Liga +</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1778,7 +1756,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1803,48 +1781,48 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>40</v>
+        <v>34.6</v>
       </c>
       <c r="W15" t="n">
-        <v>24.9</v>
+        <v>32.7</v>
       </c>
       <c r="X15" t="n">
-        <v>35</v>
+        <v>32.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>57.9</v>
+        <v>47.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>35.2</v>
+        <v>26.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>437</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>FK Neftekhimik</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="E16" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="F16" t="n">
-        <v>15.5</v>
+        <v>4.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1853,11 +1831,11 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>268</v>
+        <v>37</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Italy Serie A +</t>
+          <t>Russia First League +</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1892,61 +1870,61 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>44</v>
+        <v>43.2</v>
       </c>
       <c r="W16" t="n">
-        <v>20.9</v>
+        <v>35.1</v>
       </c>
       <c r="X16" t="n">
-        <v>35.1</v>
+        <v>21.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>63.1</v>
+        <v>43.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>42.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>268</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Shinnik Yaroslavl</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>270</v>
+        <v>66</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Italy Serie A +</t>
+          <t>Russia First League +</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1981,48 +1959,48 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>43.7</v>
+        <v>34.8</v>
       </c>
       <c r="W17" t="n">
-        <v>20.7</v>
+        <v>27.3</v>
       </c>
       <c r="X17" t="n">
-        <v>35.6</v>
+        <v>37.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>63.3</v>
+        <v>51.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>42.6</v>
+        <v>27.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>270</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jong PSV U21</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jong AZ</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2031,11 +2009,11 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>282</v>
+        <v>41</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie +</t>
+          <t>Spain La Liga +</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2045,7 +2023,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2070,61 +2048,61 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="W18" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="X18" t="n">
-        <v>35.1</v>
+        <v>34.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>42.9</v>
+        <v>41.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>282</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jong Utrecht</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jong Ajax</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F19" t="n">
         <v>2.2</v>
       </c>
-      <c r="E19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.8</v>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>303</v>
+        <v>38</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie +</t>
+          <t>Spain Segunda División +</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2134,7 +2112,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2159,61 +2137,61 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>44.2</v>
+        <v>31.6</v>
       </c>
       <c r="W19" t="n">
-        <v>20.1</v>
+        <v>31.6</v>
       </c>
       <c r="X19" t="n">
-        <v>35.6</v>
+        <v>36.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>63.4</v>
+        <v>50</v>
       </c>
       <c r="Z19" t="n">
-        <v>40.9</v>
+        <v>26.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>303</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC Braga</t>
+          <t>Atletico Torque</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="E20" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>270</v>
+        <v>64</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga +</t>
+          <t>Uruguay Primera División +</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2223,7 +2201,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2248,66 +2226,64 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>44.1</v>
+        <v>29.7</v>
       </c>
       <c r="W20" t="n">
-        <v>21.1</v>
+        <v>29.7</v>
       </c>
       <c r="X20" t="n">
-        <v>34.8</v>
+        <v>40.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="Z20" t="n">
-        <v>41.9</v>
+        <v>28.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>270</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>6.8</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
       <c r="I21" t="n">
-        <v>415</v>
+        <v>2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga +</t>
+          <t>Brazil Serie A +</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2337,71 +2313,69 @@
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>40.2</v>
+        <v>100</v>
       </c>
       <c r="W21" t="n">
-        <v>24.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>35.7</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="Z21" t="n">
-        <v>35.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estrela</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
       <c r="I22" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga +</t>
+          <t>Italy Serie A +</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2425,72 +2399,60 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X22" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>35.9</v>
-      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FC Porto B</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="E23" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
       <c r="I23" t="n">
-        <v>296</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Portugal Segunda Liga +</t>
+          <t>Italy Serie A +</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2515,71 +2477,69 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>41.6</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>20.3</v>
+        <v>100</v>
       </c>
       <c r="X23" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>63.2</v>
+        <v>100</v>
       </c>
       <c r="Z23" t="n">
-        <v>41.6</v>
+        <v>100</v>
       </c>
       <c r="AA23" t="n">
-        <v>296</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sporting CP B</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lusitânia Lourosa</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="E24" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="F24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
       <c r="I24" t="n">
-        <v>296</v>
+        <v>2</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Portugal Segunda Liga +</t>
+          <t>Italy Serie A +</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2604,71 +2564,69 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>43.9</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>32.8</v>
+        <v>100</v>
       </c>
       <c r="Y24" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="Z24" t="n">
-        <v>39.5</v>
+        <v>100</v>
       </c>
       <c r="AA24" t="n">
-        <v>296</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Jong PSV U21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Jong AZ</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
         <v>2.3</v>
       </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
       <c r="I25" t="n">
-        <v>368</v>
+        <v>9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Russia First League +</t>
+          <t>Netherlands Eerste Divisie +</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2693,66 +2651,64 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>40.5</v>
+        <v>22.2</v>
       </c>
       <c r="W25" t="n">
-        <v>22.3</v>
+        <v>33.3</v>
       </c>
       <c r="X25" t="n">
-        <v>37.2</v>
+        <v>44.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>59.5</v>
+        <v>55.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>37.2</v>
+        <v>44.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>368</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FK Neftekhimik</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="F26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
       <c r="I26" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Russia First League +</t>
+          <t>Norway Eliteserien +</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2781,72 +2737,60 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X26" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>39.9</v>
-      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shinnik Yaroslavl</t>
+          <t>SC Braga</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="F27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
       <c r="I27" t="n">
-        <v>335</v>
+        <v>2</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Russia First League +</t>
+          <t>Portugal Primeira Liga +</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2871,66 +2815,64 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>42.1</v>
+        <v>50</v>
       </c>
       <c r="W27" t="n">
-        <v>22.4</v>
+        <v>50</v>
       </c>
       <c r="X27" t="n">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>60.6</v>
+        <v>50</v>
       </c>
       <c r="Z27" t="n">
-        <v>39.1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>335</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FC Sochi</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="E28" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="F28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>2</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
-        <v>308</v>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Russia First League +</t>
+          <t>Turkey Süper Lig +</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2960,556 +2902,22 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>41.6</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>21.8</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>36.7</v>
+        <v>100</v>
       </c>
       <c r="Y28" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="Z28" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="AA28" t="n">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Celta de Vigo II</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Eibar</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="n">
-        <v>307</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Spain Segunda División +</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="W29" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Gaziantep FK</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Fenerbahçe</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>270</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Turkey Süper Lig +</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="W30" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="X30" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Atletico Torque</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Liverpool Montevideo</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F31" t="n">
         <v>2</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="n">
-        <v>333</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Uruguay Primera División +</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X31" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Esteghlal FC</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Al Sadd</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
-        <v>326</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>World AFC Champions League Elite +</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="X32" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Al-Ahli Jeddah</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Pakhtakor</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
-        <v>269</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>World AFC Champions League Elite +</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="W33" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X33" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Al-Qadisiyah FC</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Al-Wasl FC</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F34" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
-        <v>271</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>World AFC Champions League Elite +</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="X34" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,35 +561,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC Porto B</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Portugal Segunda Liga +</t>
+          <t>Germany 3. Liga +</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -624,48 +624,48 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>19.2</v>
+        <v>80</v>
       </c>
       <c r="W2" t="n">
-        <v>15.4</v>
+        <v>10</v>
       </c>
       <c r="X2" t="n">
-        <v>65.40000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>69.2</v>
+        <v>70</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.5</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sporting CP B</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lusitânia Lourosa</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Portugal Segunda Liga +</t>
+          <t>Scotland Premiership +</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -713,66 +713,66 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>46.2</v>
+        <v>72.7</v>
       </c>
       <c r="W3" t="n">
-        <v>42.3</v>
+        <v>9.1</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>18.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>30.8</v>
+        <v>63.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.4</v>
+        <v>36.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Russia First League +</t>
+          <t>England Championship +</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -802,48 +802,48 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>30.9</v>
+        <v>63</v>
       </c>
       <c r="W4" t="n">
-        <v>23.4</v>
+        <v>22.2</v>
       </c>
       <c r="X4" t="n">
-        <v>45.7</v>
+        <v>14.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>50</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.4</v>
+        <v>37</v>
       </c>
       <c r="AA4" t="n">
-        <v>94</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>SSV Jahn Regensburg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FC Sochi</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -852,16 +852,16 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Russia First League +</t>
+          <t>Germany 3. Liga +</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -891,66 +891,66 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>25.6</v>
+        <v>22.7</v>
       </c>
       <c r="W5" t="n">
-        <v>28.2</v>
+        <v>21.2</v>
       </c>
       <c r="X5" t="n">
-        <v>46.2</v>
+        <v>56.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>56.4</v>
+        <v>57.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>28.2</v>
+        <v>30.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Nautico Recife</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Operario-PR</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Argentina Liga Profesional +</t>
+          <t>Brazil Serie B +</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -980,48 +980,48 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>31</v>
+        <v>49.2</v>
       </c>
       <c r="W6" t="n">
-        <v>26.2</v>
+        <v>35.4</v>
       </c>
       <c r="X6" t="n">
-        <v>42.9</v>
+        <v>15.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>40.5</v>
+        <v>46.2</v>
       </c>
       <c r="Z6" t="n">
         <v>26.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1030,21 +1030,21 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Argentina Liga Profesional +</t>
+          <t>England Championship +</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1069,48 +1069,48 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>41.7</v>
+        <v>48.9</v>
       </c>
       <c r="W7" t="n">
-        <v>25</v>
+        <v>28.9</v>
       </c>
       <c r="X7" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.3</v>
+        <v>45.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>SG Sonnenhof Grossaspach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1119,16 +1119,16 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>131</v>
+        <v>37</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Brazil Serie B +</t>
+          <t>Germany 3. Liga +</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1158,48 +1158,48 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>34.4</v>
+        <v>37.8</v>
       </c>
       <c r="W8" t="n">
-        <v>22.1</v>
+        <v>13.5</v>
       </c>
       <c r="X8" t="n">
-        <v>43.5</v>
+        <v>48.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>51.9</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.1</v>
+        <v>40.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>131</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1208,21 +1208,21 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Brazil Serie B +</t>
+          <t>Germany 3. Liga +</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1247,48 +1247,48 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>31.4</v>
+        <v>21.7</v>
       </c>
       <c r="W9" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="X9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Y9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Heart Of Midlothian</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1297,21 +1297,21 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>168</v>
+        <v>35</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Chile Primera División +</t>
+          <t>Scotland Premiership +</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1336,48 +1336,48 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>32.1</v>
+        <v>14.3</v>
       </c>
       <c r="W10" t="n">
-        <v>32.1</v>
+        <v>31.4</v>
       </c>
       <c r="X10" t="n">
-        <v>35.7</v>
+        <v>54.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>50.6</v>
+        <v>40</v>
       </c>
       <c r="Z10" t="n">
-        <v>27.4</v>
+        <v>28.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>168</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1386,16 +1386,16 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>England Premier League +</t>
+          <t>Scotland Premiership +</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1425,66 +1425,66 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>40.9</v>
+        <v>46.6</v>
       </c>
       <c r="W11" t="n">
-        <v>22.6</v>
+        <v>28.8</v>
       </c>
       <c r="X11" t="n">
-        <v>36.6</v>
+        <v>24.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>61.3</v>
+        <v>54.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>30.1</v>
+        <v>34.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RED Star FC 93</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>France Ligue 2 +</t>
+          <t>Spain La Liga +</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1514,61 +1514,61 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>33.3</v>
+        <v>48.6</v>
       </c>
       <c r="W12" t="n">
-        <v>30.9</v>
+        <v>21</v>
       </c>
       <c r="X12" t="n">
-        <v>35.8</v>
+        <v>30.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>49.1</v>
+        <v>55.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>24.2</v>
+        <v>29.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>165</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jong Utrecht</t>
+          <t>SV Meppen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jong Ajax</t>
+          <t>FC Viktoria Köln</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F13" t="n">
         <v>2.2</v>
       </c>
-      <c r="E13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.8</v>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie +</t>
+          <t>Germany 3. Liga +</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1603,61 +1603,61 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>43.8</v>
+        <v>20</v>
       </c>
       <c r="W13" t="n">
-        <v>15.6</v>
+        <v>40</v>
       </c>
       <c r="X13" t="n">
-        <v>40.6</v>
+        <v>40</v>
       </c>
       <c r="Y13" t="n">
-        <v>65.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="Z13" t="n">
-        <v>31.2</v>
+        <v>43.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga +</t>
+          <t>Spain La Liga +</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1692,71 +1692,69 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="W14" t="n">
-        <v>29.1</v>
+        <v>28.6</v>
       </c>
       <c r="X14" t="n">
-        <v>37.6</v>
+        <v>28.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>51.1</v>
+        <v>61.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>23.4</v>
+        <v>38.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>141</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estrela</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
       <c r="I15" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga +</t>
+          <t>Brazil Serie B +</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1781,66 +1779,64 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>34.6</v>
+        <v>100</v>
       </c>
       <c r="W15" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>47.1</v>
+        <v>100</v>
       </c>
       <c r="Z15" t="n">
-        <v>26.1</v>
+        <v>100</v>
       </c>
       <c r="AA15" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FK Neftekhimik</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
       <c r="I16" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Russia First League +</t>
+          <t>Netherlands Eredivisie +</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1869,67 +1865,55 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>24.3</v>
-      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shinnik Yaroslavl</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
       <c r="I17" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Russia First League +</t>
+          <t>Scotland Championship +</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1959,57 +1943,55 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>34.8</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>27.3</v>
+        <v>14.3</v>
       </c>
       <c r="X17" t="n">
-        <v>37.9</v>
+        <v>85.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>51.5</v>
+        <v>57.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>27.3</v>
+        <v>14.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.9</v>
+        <v>11.5</v>
       </c>
       <c r="E18" t="n">
-        <v>3.9</v>
+        <v>6.9</v>
       </c>
       <c r="F18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
       <c r="I18" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2018,12 +2000,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2047,72 +2029,60 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>22</v>
-      </c>
-      <c r="X18" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>41.5</v>
-      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Vasco DA Gama</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
       <c r="I19" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Spain Segunda División +</t>
+          <t>World CONMEBOL Sudamericana +</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2137,786 +2107,21 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>31.6</v>
+        <v>100</v>
       </c>
       <c r="W19" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>36.8</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>50</v>
       </c>
       <c r="Z19" t="n">
-        <v>26.3</v>
+        <v>50</v>
       </c>
       <c r="AA19" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Atletico Torque</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Liverpool Montevideo</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="n">
-        <v>64</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Uruguay Primera División +</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="X20" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Brazil Serie A +</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
-        <v>100</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Italy Serie A +</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Italy Serie A +</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>100</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Italy Serie A +</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Jong PSV U21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Jong AZ</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E25" t="n">
-        <v>4</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>9</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Netherlands Eerste Divisie +</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W25" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="X25" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bodo/Glimt</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sandefjord</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Norway Eliteserien +</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SC Braga</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F27" t="n">
-        <v>7</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga +</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="n">
-        <v>50</v>
-      </c>
-      <c r="W27" t="n">
-        <v>50</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Gaziantep FK</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Fenerbahçe</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Turkey Süper Lig +</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA28" t="n">
         <v>2</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1090,7 +1090,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,7 +1268,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1446,7 +1446,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1535,7 +1535,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1713,7 +1713,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1877,7 +1877,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1964,7 +1964,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2041,7 +2041,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,40 +556,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="F2" t="n">
-        <v>7.5</v>
+        <v>17</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Germany 3. Liga +</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -621,64 +623,68 @@
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>69.8</v>
+      </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>80</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>10</v>
+        <v>12.8</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>12.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>46.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Jagiellonia</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Scotland Premiership +</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -710,69 +716,73 @@
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>65.8</v>
+      </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>72.7</v>
+        <v>64.3</v>
       </c>
       <c r="W3" t="n">
-        <v>9.1</v>
+        <v>20.4</v>
       </c>
       <c r="X3" t="n">
-        <v>18.2</v>
+        <v>15.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>63.6</v>
+        <v>65.8</v>
       </c>
       <c r="Z3" t="n">
         <v>36.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Spartak Moscow</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
       <c r="I4" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>England Championship +</t>
+          <t>Russia Premier League</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -799,25 +809,27 @@
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>51.1</v>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="W4" t="n">
-        <v>22.2</v>
+        <v>29.3</v>
       </c>
       <c r="X4" t="n">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>70.40000000000001</v>
+        <v>51.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>37</v>
+        <v>27.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -828,35 +840,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SSV Jahn Regensburg</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
       <c r="I5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Germany 3. Liga +</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -866,7 +880,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -888,69 +902,73 @@
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>51.9</v>
+      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>22.7</v>
+        <v>38.6</v>
       </c>
       <c r="W5" t="n">
-        <v>21.2</v>
+        <v>25.7</v>
       </c>
       <c r="X5" t="n">
-        <v>56.1</v>
+        <v>35.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>57.6</v>
+        <v>51.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nautico Recife</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Operario-PR</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Brazil Serie B +</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -977,69 +995,73 @@
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>59.1</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>49.2</v>
+        <v>53.8</v>
       </c>
       <c r="W6" t="n">
-        <v>35.4</v>
+        <v>21.6</v>
       </c>
       <c r="X6" t="n">
-        <v>15.4</v>
+        <v>24.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>46.2</v>
+        <v>59.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
       <c r="I7" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>England Championship +</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1066,64 +1088,68 @@
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>60.1</v>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>48.9</v>
+        <v>47.7</v>
       </c>
       <c r="W7" t="n">
-        <v>28.9</v>
+        <v>20.7</v>
       </c>
       <c r="X7" t="n">
-        <v>22.2</v>
+        <v>31.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>45.6</v>
+        <v>60.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>22.2</v>
+        <v>27.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SG Sonnenhof Grossaspach</t>
+          <t>Ararat-Armenia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.1</v>
+        <v>5.2</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>원정승</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
       <c r="I8" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Germany 3. Liga +</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1133,7 +1159,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1155,74 +1181,74 @@
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>60</v>
+      </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z8" t="n">
         <v>37.8</v>
       </c>
-      <c r="W8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>40.5</v>
-      </c>
       <c r="AA8" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5</v>
+        <v>14.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
       <c r="I9" t="n">
         <v>60</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Germany 3. Liga +</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1244,22 +1270,24 @@
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>55</v>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>21.7</v>
+        <v>44.8</v>
       </c>
       <c r="W9" t="n">
-        <v>33.3</v>
+        <v>23.3</v>
       </c>
       <c r="X9" t="n">
-        <v>45</v>
+        <v>31.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z9" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="AA9" t="n">
         <v>60</v>
@@ -1268,50 +1296,48 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Heart Of Midlothian</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="E10" t="n">
         <v>3.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
       <c r="I10" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Scotland Premiership +</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1333,69 +1359,69 @@
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>55.4</v>
+      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>14.3</v>
+        <v>46.1</v>
       </c>
       <c r="W10" t="n">
-        <v>31.4</v>
+        <v>25</v>
       </c>
       <c r="X10" t="n">
-        <v>54.3</v>
+        <v>28.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>40</v>
+        <v>55.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>02:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
       <c r="I11" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Scotland Premiership +</t>
+          <t>Russia Premier League</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1422,74 +1448,74 @@
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>53.9</v>
+      </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>46.6</v>
+        <v>50.1</v>
       </c>
       <c r="W11" t="n">
-        <v>28.8</v>
+        <v>31.3</v>
       </c>
       <c r="X11" t="n">
-        <v>24.7</v>
+        <v>18.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>54.8</v>
+        <v>53.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
       <c r="I12" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Spain La Liga +</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1511,74 +1537,74 @@
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>49.9</v>
+      </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>48.6</v>
+        <v>26</v>
       </c>
       <c r="W12" t="n">
-        <v>21</v>
+        <v>29.1</v>
       </c>
       <c r="X12" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="Z12" t="n">
         <v>30.5</v>
       </c>
-      <c r="Y12" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>29.5</v>
-      </c>
       <c r="AA12" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SV Meppen</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FC Viktoria Köln</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="E13" t="n">
         <v>3.7</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>무승부</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
       <c r="I13" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Germany 3. Liga +</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1600,69 +1626,69 @@
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>50.2</v>
+      </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>20</v>
+        <v>46.4</v>
       </c>
       <c r="W13" t="n">
-        <v>40</v>
+        <v>25.6</v>
       </c>
       <c r="X13" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="Y13" t="n">
-        <v>60</v>
+        <v>50.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>43.3</v>
+        <v>27.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>4.3</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Spain La Liga +</t>
+          <t>World CONMEBOL Sudamericana</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1689,72 +1715,74 @@
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>43.7</v>
+      </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>42.9</v>
+        <v>36.4</v>
       </c>
       <c r="W14" t="n">
-        <v>28.6</v>
+        <v>49.8</v>
       </c>
       <c r="X14" t="n">
-        <v>28.6</v>
+        <v>13.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>61.9</v>
+        <v>43.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>38.1</v>
+        <v>25.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="F15" t="n">
-        <v>10.2</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Brazil Serie B +</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1776,72 +1804,74 @@
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>51.5</v>
+      </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>100</v>
+        <v>28.8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>40.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>100</v>
+        <v>51.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>100</v>
+        <v>30.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>02:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="E16" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="F16" t="n">
-        <v>17.2</v>
+        <v>1.9</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie +</t>
+          <t>Russia Premier League</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1863,57 +1893,69 @@
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>57.5</v>
+      </c>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>30.7</v>
+      </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Rot-Weiß Essen</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Scotland Championship +</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1940,67 +1982,69 @@
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>54.1</v>
+      </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="W17" t="n">
-        <v>14.3</v>
+        <v>22.6</v>
       </c>
       <c r="X17" t="n">
-        <v>85.7</v>
+        <v>48.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>57.1</v>
+        <v>54.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.3</v>
+        <v>28.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="E18" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Spain La Liga +</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2027,57 +2071,69 @@
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>56.5</v>
+      </c>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>32.6</v>
+      </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vasco DA Gama</t>
+          <t>FC Ingolstadt 04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="F19" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>World CONMEBOL Sudamericana +</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2104,25 +2160,838 @@
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>55.4</v>
+      </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>100</v>
+        <v>36.5</v>
       </c>
       <c r="W19" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Preußen Münster</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FC Saarbrücken</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
         <v>0</v>
       </c>
-      <c r="X19" t="n">
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>54</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X20" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
         <v>0</v>
       </c>
-      <c r="Y19" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="I21" t="n">
+        <v>60</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>World UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fortuna Köln</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SV Wehen</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>60</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>54</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X22" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>48</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Colombia Primera A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="X23" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LDU de Quito</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>24</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="X25" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruna</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>60</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="X26" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FK Yenisey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Arsenal Tula</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>60</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Russia First League</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>33</v>
+      </c>
+      <c r="N27" t="n">
+        <v>42</v>
+      </c>
+      <c r="O27" t="n">
+        <v>25</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>30</v>
+      </c>
+      <c r="X27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rodina Moskva</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Rubin</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>60</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Russia Premier League</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>36</v>
+      </c>
+      <c r="W28" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AG28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,100 +454,130 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>신뢰도</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>판정근거</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>예상확률</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>총경기수</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>리그</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>신호등급</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>정배위치</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>FB_홈승확률</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>FB_무승부확률</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FB_원정승확률</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>최종_홈승확률</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>최종_무승부확률</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>최종_원정승확률</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>유효표본</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>FB_예상점수</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>FB_예측결과</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>FB_평균득점</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>오버25예측</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>오버25구간실적</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>오버35예측</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>유사_홈승실적</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>유사_무실적</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>유사_원정실적</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>유사_오버25</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>유사_오버35</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>유사경기수</t>
         </is>
@@ -583,66 +613,88 @@
           <t>홈승</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>모든 모델 합의</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>60</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>World UEFA Europa League</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="T2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="U2" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
         <v>69.8</v>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AC2" t="n">
         <v>12.8</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AD2" t="n">
         <v>12.6</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="n">
         <v>69.8</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AF2" t="n">
         <v>46.9</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AG2" t="n">
         <v>60</v>
       </c>
     </row>
@@ -676,66 +728,88 @@
           <t>홈승</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>모든 모델 합의</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>60</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>World UEFA Europa League</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="T3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>44.52</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
         <v>65.8</v>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="n">
         <v>64.3</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AC3" t="n">
         <v>20.4</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AD3" t="n">
         <v>15.3</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AE3" t="n">
         <v>65.8</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AF3" t="n">
         <v>36.4</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AG3" t="n">
         <v>60</v>
       </c>
     </row>
@@ -769,66 +843,88 @@
           <t>홈승</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>모든 모델 합의</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
-        <v>60</v>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Russia Premier League</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="T4" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
         <v>51.1</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
         <v>55</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AC4" t="n">
         <v>29.3</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AD4" t="n">
         <v>15.7</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AE4" t="n">
         <v>51.1</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AF4" t="n">
         <v>27.9</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AG4" t="n">
         <v>60</v>
       </c>
     </row>
@@ -862,66 +958,88 @@
           <t>홈승</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2개 이상 모델 합의</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>60</v>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>60</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Spain La Liga</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>21.8</v>
+      </c>
       <c r="T5" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
         <v>51.9</v>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
         <v>38.6</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AC5" t="n">
         <v>25.7</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AD5" t="n">
         <v>35.7</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AE5" t="n">
         <v>51.9</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AF5" t="n">
         <v>30.2</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AG5" t="n">
         <v>60</v>
       </c>
     </row>
@@ -955,66 +1073,88 @@
           <t>홈승</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2개 이상 모델 합의</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>World UEFA Europa League</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>22.2</v>
+      </c>
       <c r="T6" t="n">
+        <v>20</v>
+      </c>
+      <c r="U6" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
         <v>59.1</v>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
         <v>53.8</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AC6" t="n">
         <v>21.6</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AD6" t="n">
         <v>24.6</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AE6" t="n">
         <v>59.1</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AF6" t="n">
         <v>29.9</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AG6" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1048,66 +1188,88 @@
           <t>홈승</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2개 이상 모델 합의</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="n">
-        <v>60</v>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Germany 3. Liga</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20.7</v>
+      </c>
       <c r="T7" t="n">
+        <v>23</v>
+      </c>
+      <c r="U7" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
         <v>60.1</v>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
         <v>47.7</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AC7" t="n">
         <v>20.7</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AD7" t="n">
         <v>31.6</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AE7" t="n">
         <v>60.1</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AF7" t="n">
         <v>27.7</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AG7" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1141,66 +1303,88 @@
           <t>원정승</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>최소 기준 통과</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="n">
-        <v>60</v>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>60</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>World UEFA Europa League</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="S8" t="n">
+        <v>22.5</v>
+      </c>
       <c r="T8" t="n">
-        <v>60</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
         <v>28.2</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AC8" t="n">
         <v>21.1</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AD8" t="n">
         <v>50.8</v>
       </c>
-      <c r="Y8" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AE8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF8" t="n">
         <v>37.8</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AG8" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1230,66 +1414,88 @@
         <v>31</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="n">
-        <v>60</v>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>60</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Spain La Liga</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>12.7</v>
+      </c>
       <c r="T9" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
         <v>55</v>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="n">
         <v>44.8</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AC9" t="n">
         <v>23.3</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AD9" t="n">
         <v>31.9</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AE9" t="n">
         <v>55</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AF9" t="n">
         <v>33.7</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AG9" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1319,66 +1525,88 @@
         <v>4.6</v>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>48</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25.2</v>
+      </c>
       <c r="T10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
         <v>55.4</v>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="n">
         <v>46.1</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AC10" t="n">
         <v>25</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AD10" t="n">
         <v>28.9</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AE10" t="n">
         <v>55.4</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AF10" t="n">
         <v>27.6</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AG10" t="n">
         <v>48</v>
       </c>
     </row>
@@ -1408,66 +1636,88 @@
         <v>4</v>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="n">
-        <v>60</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>60</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Russia Premier League</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>27.2</v>
+      </c>
       <c r="T11" t="n">
+        <v>22</v>
+      </c>
+      <c r="U11" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
         <v>53.9</v>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="n">
         <v>50.1</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AC11" t="n">
         <v>31.3</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AD11" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AE11" t="n">
         <v>53.9</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AF11" t="n">
         <v>34.1</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AG11" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1497,66 +1747,88 @@
         <v>1.9</v>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="n">
-        <v>60</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>60</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>World UEFA Europa League</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>26</v>
+      </c>
+      <c r="S12" t="n">
+        <v>26.5</v>
+      </c>
       <c r="T12" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
         <v>49.9</v>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="n">
         <v>26</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AC12" t="n">
         <v>29.1</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AD12" t="n">
         <v>45</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AE12" t="n">
         <v>49.9</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AF12" t="n">
         <v>30.5</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AG12" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1586,66 +1858,88 @@
         <v>3.5</v>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="n">
-        <v>60</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>60</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>World UEFA Europa League</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>46</v>
+      </c>
+      <c r="S13" t="n">
+        <v>26.1</v>
+      </c>
       <c r="T13" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
         <v>50.2</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="n">
         <v>46.4</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AC13" t="n">
         <v>25.6</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AD13" t="n">
         <v>28</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AE13" t="n">
         <v>50.2</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AF13" t="n">
         <v>27.8</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AG13" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1675,66 +1969,88 @@
         <v>4.3</v>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>27</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>World CONMEBOL Sudamericana</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="S14" t="n">
+        <v>35.4</v>
+      </c>
       <c r="T14" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
         <v>43.7</v>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="n">
         <v>36.4</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AC14" t="n">
         <v>49.8</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AD14" t="n">
         <v>13.9</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AE14" t="n">
         <v>43.7</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AF14" t="n">
         <v>25.4</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AG14" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1764,66 +2080,88 @@
         <v>2</v>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="n">
-        <v>60</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>60</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>World UEFA Europa League</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>26.9</v>
+      </c>
       <c r="T15" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
         <v>51.5</v>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="n">
         <v>28.8</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AC15" t="n">
         <v>30.8</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AD15" t="n">
         <v>40.4</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AE15" t="n">
         <v>51.5</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AF15" t="n">
         <v>30.4</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AG15" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1853,66 +2191,88 @@
         <v>1.9</v>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="n">
-        <v>60</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>Russia Premier League</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>26</v>
+      </c>
+      <c r="S16" t="n">
+        <v>28.9</v>
+      </c>
       <c r="T16" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
         <v>57.5</v>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="n">
         <v>31.9</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AC16" t="n">
         <v>32.1</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AD16" t="n">
         <v>36</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AE16" t="n">
         <v>57.5</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AF16" t="n">
         <v>30.7</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AG16" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1942,66 +2302,88 @@
         <v>2.1</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
-        <v>60</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>60</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>Germany 3. Liga</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="S17" t="n">
+        <v>24.4</v>
+      </c>
       <c r="T17" t="n">
+        <v>45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
         <v>54.1</v>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="n">
         <v>28.6</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AC17" t="n">
         <v>22.6</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AD17" t="n">
         <v>48.8</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AE17" t="n">
         <v>54.1</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AF17" t="n">
         <v>28.4</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AG17" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2031,66 +2413,88 @@
         <v>2</v>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="n">
-        <v>60</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>60</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>World UEFA Europa League</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="S18" t="n">
+        <v>27.6</v>
+      </c>
       <c r="T18" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
         <v>56.5</v>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="n">
         <v>33.1</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AC18" t="n">
         <v>26.5</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AD18" t="n">
         <v>40.4</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AE18" t="n">
         <v>56.5</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AF18" t="n">
         <v>32.6</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AG18" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2120,66 +2524,88 @@
         <v>3.3</v>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="n">
-        <v>60</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>60</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>Germany 3. Liga</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>24.5</v>
+      </c>
       <c r="T19" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
         <v>55.4</v>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="n">
         <v>36.5</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AC19" t="n">
         <v>24.2</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AD19" t="n">
         <v>39.3</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AE19" t="n">
         <v>55.4</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AF19" t="n">
         <v>27.4</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AG19" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2209,66 +2635,88 @@
         <v>2.2</v>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="n">
-        <v>60</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>60</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>Germany 3. Liga</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25.3</v>
+      </c>
       <c r="T20" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
         <v>54</v>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="n">
         <v>28.6</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AC20" t="n">
         <v>22.8</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AD20" t="n">
         <v>48.6</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AE20" t="n">
         <v>54</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AF20" t="n">
         <v>28.3</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AG20" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2298,66 +2746,88 @@
         <v>2.3</v>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
         <v>0</v>
       </c>
-      <c r="I21" t="n">
-        <v>60</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>60</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>World UEFA Europa League</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>26.5</v>
+      </c>
       <c r="T21" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
         <v>60.3</v>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="n">
         <v>27.7</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AC21" t="n">
         <v>26.8</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AD21" t="n">
         <v>45.5</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AE21" t="n">
         <v>60.3</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AF21" t="n">
         <v>29.2</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AG21" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2387,66 +2857,88 @@
         <v>2.4</v>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="n">
-        <v>60</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>60</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>Germany 3. Liga</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="S22" t="n">
+        <v>26.1</v>
+      </c>
       <c r="T22" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
         <v>54</v>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="n">
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="n">
         <v>28.9</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AC22" t="n">
         <v>22.9</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AD22" t="n">
         <v>48.2</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AE22" t="n">
         <v>54</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AF22" t="n">
         <v>28.1</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AG22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2476,66 +2968,88 @@
         <v>3.7</v>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>48</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Colombia Primera A</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>41</v>
+      </c>
+      <c r="S23" t="n">
+        <v>35.3</v>
+      </c>
       <c r="T23" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="U23" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
         <v>42.1</v>
       </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="n">
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="n">
         <v>31.4</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AC23" t="n">
         <v>47.4</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AD23" t="n">
         <v>21.2</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AE23" t="n">
         <v>42.1</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AF23" t="n">
         <v>22.3</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AG23" t="n">
         <v>48</v>
       </c>
     </row>
@@ -2565,66 +3079,88 @@
         <v>2.1</v>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
-        <v>60</v>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>60</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>Spain La Liga</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="S24" t="n">
+        <v>28.3</v>
+      </c>
       <c r="T24" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
         <v>52.6</v>
       </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="n">
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="n">
         <v>36.1</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AC24" t="n">
         <v>29.9</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AD24" t="n">
         <v>34</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AE24" t="n">
         <v>52.6</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AF24" t="n">
         <v>30.9</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AG24" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2654,66 +3190,88 @@
         <v>2.8</v>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>24</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>World CONMEBOL Libertadores</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>21.6</v>
+      </c>
       <c r="T25" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
         <v>49.7</v>
       </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="n">
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="n">
         <v>47.4</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AC25" t="n">
         <v>5.6</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AD25" t="n">
         <v>47</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AE25" t="n">
         <v>49.7</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AF25" t="n">
         <v>27.2</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AG25" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2743,66 +3301,88 @@
         <v>3</v>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="n">
-        <v>60</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="n">
+        <v>60</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Spain La Liga</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>30.7</v>
+      </c>
       <c r="T26" t="n">
+        <v>31</v>
+      </c>
+      <c r="U26" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
         <v>46.2</v>
       </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="n">
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="n">
         <v>39.6</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AC26" t="n">
         <v>30.7</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AD26" t="n">
         <v>29.7</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AE26" t="n">
         <v>46.2</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AF26" t="n">
         <v>23.6</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AG26" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2832,76 +3412,98 @@
         <v>3</v>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
         <v>0</v>
       </c>
-      <c r="I27" t="n">
-        <v>60</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="n">
+        <v>60</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Russia First League</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>33</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>42</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>25</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S27" t="n">
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
         <v>32.3</v>
       </c>
-      <c r="T27" t="n">
+      <c r="Z27" t="n">
         <v>53.8</v>
       </c>
-      <c r="U27" t="n">
+      <c r="AA27" t="n">
         <v>14.3</v>
       </c>
-      <c r="V27" t="n">
+      <c r="AB27" t="n">
         <v>38.9</v>
       </c>
-      <c r="W27" t="n">
+      <c r="AC27" t="n">
         <v>30</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AD27" t="n">
         <v>31.1</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AE27" t="n">
         <v>53.8</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AF27" t="n">
         <v>29.8</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AG27" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2931,66 +3533,88 @@
         <v>2.5</v>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
         <v>0</v>
       </c>
-      <c r="I28" t="n">
-        <v>60</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="n">
+        <v>60</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Russia Premier League</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>30.7</v>
+      </c>
       <c r="T28" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
         <v>55.7</v>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="n">
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="n">
         <v>36</v>
       </c>
-      <c r="W28" t="n">
+      <c r="AC28" t="n">
         <v>32.8</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AD28" t="n">
         <v>31.1</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AE28" t="n">
         <v>55.7</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AF28" t="n">
         <v>33</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AG28" t="n">
         <v>60</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG28"/>
+  <dimension ref="A1:AG22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,22 +591,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6</v>
+        <v>5.2</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>7.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -648,16 +648,16 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>80.09999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="S2" t="n">
-        <v>11.7</v>
+        <v>19.7</v>
       </c>
       <c r="T2" t="n">
-        <v>8.199999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="U2" t="n">
-        <v>39.65</v>
+        <v>8.52</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -676,26 +676,26 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>69.8</v>
+        <v>51.2</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>74.59999999999999</v>
+        <v>49.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.8</v>
+        <v>21.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.6</v>
+        <v>28.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>69.8</v>
+        <v>51.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>46.9</v>
+        <v>27.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -706,22 +706,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jagiellonia</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -730,19 +730,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>모든 모델 합의</t>
+          <t>2개 이상 모델 합의</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -763,16 +763,16 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>67.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>20.1</v>
+        <v>16.1</v>
       </c>
       <c r="T3" t="n">
-        <v>12.7</v>
+        <v>14.8</v>
       </c>
       <c r="U3" t="n">
-        <v>44.52</v>
+        <v>6.11</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -791,52 +791,52 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>65.8</v>
+        <v>53.3</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>64.3</v>
+        <v>51.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.3</v>
+        <v>27.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>65.8</v>
+        <v>53.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>36.4</v>
+        <v>29.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spartak Moscow</t>
+          <t>Nizhny Novgorod</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.4</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="F4" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -845,12 +845,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>모든 모델 합의</t>
+          <t>2개 이상 모델 합의</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -861,12 +861,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Russia Premier League</t>
+          <t>Russia First League</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -878,16 +878,16 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>65.3</v>
+        <v>58.4</v>
       </c>
       <c r="S4" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="T4" t="n">
-        <v>12.2</v>
+        <v>18.1</v>
       </c>
       <c r="U4" t="n">
-        <v>15.47</v>
+        <v>12.19</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -906,23 +906,23 @@
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>51.1</v>
+        <v>49.4</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>55</v>
+        <v>44.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>29.3</v>
+        <v>27.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.7</v>
+        <v>27.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>51.1</v>
+        <v>49.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>27.9</v>
+        <v>30.6</v>
       </c>
       <c r="AG4" t="n">
         <v>60</v>
@@ -931,27 +931,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Lillestrom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="F5" t="n">
-        <v>8.699999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -972,11 +972,11 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -993,16 +993,16 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>58.1</v>
+        <v>57.6</v>
       </c>
       <c r="S5" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="T5" t="n">
-        <v>20.1</v>
+        <v>21.3</v>
       </c>
       <c r="U5" t="n">
-        <v>9.699999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1021,52 +1021,52 @@
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>51.9</v>
+        <v>50</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>38.6</v>
+        <v>48.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>25.7</v>
+        <v>21.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>35.7</v>
+        <v>29.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>51.9</v>
+        <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>30.2</v>
+        <v>26.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="F6" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2개 이상 모델 합의</t>
+          <t>최소 기준 통과</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Russia First League</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1108,16 +1108,16 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>57.8</v>
+        <v>54.1</v>
       </c>
       <c r="S6" t="n">
-        <v>22.2</v>
+        <v>26.3</v>
       </c>
       <c r="T6" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="U6" t="n">
-        <v>44.14</v>
+        <v>16.23</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1136,23 +1136,23 @@
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>59.1</v>
+        <v>49.4</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>53.8</v>
+        <v>42.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.6</v>
+        <v>29.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>24.6</v>
+        <v>28.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>59.1</v>
+        <v>49.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="AG6" t="n">
         <v>60</v>
@@ -1161,78 +1161,74 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>1899 Hoffenheim</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2개 이상 모델 합의</t>
+          <t>확률·격차·표본·합의 기준 미달</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>56.3</v>
+        <v>21.8</v>
       </c>
       <c r="S7" t="n">
-        <v>20.7</v>
+        <v>19.9</v>
       </c>
       <c r="T7" t="n">
-        <v>23</v>
+        <v>58.3</v>
       </c>
       <c r="U7" t="n">
-        <v>18.46</v>
+        <v>2.92</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1251,66 +1247,62 @@
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>60.1</v>
+        <v>53.4</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
-        <v>47.7</v>
+        <v>39.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>31.6</v>
+        <v>39.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>60.1</v>
+        <v>53.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>27.7</v>
+        <v>32.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ararat-Armenia</t>
+          <t>FK Orenburg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>FK Krasnodar</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>최소 기준 통과</t>
+          <t>확률·격차·표본·합의 기준 미달</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1321,12 +1313,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Russia Premier League</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>⏭</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1334,29 +1326,35 @@
           <t>원정정배</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P8" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>58</v>
+      </c>
       <c r="R8" t="n">
-        <v>21.9</v>
+        <v>19</v>
       </c>
       <c r="S8" t="n">
-        <v>22.5</v>
+        <v>29</v>
       </c>
       <c r="T8" t="n">
-        <v>55.6</v>
+        <v>52</v>
       </c>
       <c r="U8" t="n">
-        <v>41.96</v>
+        <v>9.02</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1364,25 +1362,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr"/>
+      <c r="Y8" t="n">
+        <v>57.7</v>
+      </c>
       <c r="Z8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
+        <v>54.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>35.3</v>
+      </c>
       <c r="AB8" t="n">
-        <v>28.2</v>
+        <v>33.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.1</v>
+        <v>32.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>50.8</v>
+        <v>33.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>54.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="AG8" t="n">
         <v>60</v>
@@ -1391,27 +1393,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Ferencvarosi TC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="E9" t="n">
-        <v>14.8</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -1428,11 +1430,11 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1449,16 +1451,16 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>73.8</v>
+        <v>52</v>
       </c>
       <c r="S9" t="n">
-        <v>12.7</v>
+        <v>22.6</v>
       </c>
       <c r="T9" t="n">
-        <v>13.6</v>
+        <v>25.4</v>
       </c>
       <c r="U9" t="n">
-        <v>3.01</v>
+        <v>7.36</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1477,52 +1479,52 @@
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>44.8</v>
+        <v>46.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>23.3</v>
+        <v>20.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>31.9</v>
+        <v>32.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>33.7</v>
+        <v>26.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="F10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -1539,11 +1541,11 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1560,16 +1562,16 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>51.4</v>
+        <v>51</v>
       </c>
       <c r="S10" t="n">
-        <v>25.2</v>
+        <v>22.4</v>
       </c>
       <c r="T10" t="n">
-        <v>23.4</v>
+        <v>26.6</v>
       </c>
       <c r="U10" t="n">
-        <v>21.4</v>
+        <v>7.04</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1588,52 +1590,52 @@
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>55.4</v>
+        <v>50.3</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>25</v>
+        <v>20.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>28.9</v>
+        <v>32.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>55.4</v>
+        <v>50.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>27.6</v>
+        <v>26.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E11" t="n">
         <v>3.9</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1654,7 +1656,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Russia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1671,16 +1673,16 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="S11" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="T11" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="U11" t="n">
-        <v>27.94</v>
+        <v>20.89</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1699,23 +1701,23 @@
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>53.9</v>
+        <v>52.1</v>
       </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="n">
-        <v>50.1</v>
+        <v>37.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>31.3</v>
+        <v>27.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>18.6</v>
+        <v>34.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>53.9</v>
+        <v>52.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>34.1</v>
+        <v>28.8</v>
       </c>
       <c r="AG11" t="n">
         <v>60</v>
@@ -1724,27 +1726,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>FC Orenburg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>FC Krasnodar</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -1765,7 +1767,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Russia Premier League</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1782,16 +1784,16 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>26</v>
+        <v>24.1</v>
       </c>
       <c r="S12" t="n">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
       <c r="T12" t="n">
-        <v>47.5</v>
+        <v>48.4</v>
       </c>
       <c r="U12" t="n">
-        <v>42.49</v>
+        <v>12.86</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1810,23 +1812,23 @@
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>49.9</v>
+        <v>58.5</v>
       </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="n">
-        <v>26</v>
+        <v>29.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>29.1</v>
+        <v>33.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AE12" t="n">
-        <v>49.9</v>
+        <v>58.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>30.5</v>
+        <v>32.9</v>
       </c>
       <c r="AG12" t="n">
         <v>60</v>
@@ -1835,27 +1837,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Tekstilshchik Iv.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
@@ -1876,7 +1878,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Russia First League</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1886,32 +1888,38 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="P13" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>43.6</v>
+      </c>
       <c r="R13" t="n">
-        <v>46</v>
+        <v>26.7</v>
       </c>
       <c r="S13" t="n">
-        <v>26.1</v>
+        <v>27.1</v>
       </c>
       <c r="T13" t="n">
-        <v>27.9</v>
+        <v>46.2</v>
       </c>
       <c r="U13" t="n">
-        <v>43.42</v>
+        <v>15.06</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1919,25 +1927,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>57.7</v>
+      </c>
       <c r="Z13" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="AA13" t="inlineStr"/>
+        <v>53.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>35.3</v>
+      </c>
       <c r="AB13" t="n">
-        <v>46.4</v>
+        <v>35.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>25.6</v>
+        <v>22.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>42.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>50.2</v>
+        <v>53.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>27.8</v>
+        <v>30.3</v>
       </c>
       <c r="AG13" t="n">
         <v>60</v>
@@ -1946,27 +1958,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Atletico-MG</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="F14" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
@@ -1983,11 +1995,11 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>World CONMEBOL Sudamericana</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1997,23 +2009,23 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>45.8</v>
+        <v>29.8</v>
       </c>
       <c r="S14" t="n">
-        <v>35.4</v>
+        <v>26.3</v>
       </c>
       <c r="T14" t="n">
-        <v>18.8</v>
+        <v>43.9</v>
       </c>
       <c r="U14" t="n">
-        <v>9.06</v>
+        <v>14.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2032,52 +2044,52 @@
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>43.7</v>
+        <v>53.6</v>
       </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="n">
-        <v>36.4</v>
+        <v>35.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>49.8</v>
+        <v>28.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.9</v>
+        <v>35.9</v>
       </c>
       <c r="AE14" t="n">
-        <v>43.7</v>
+        <v>53.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>25.4</v>
+        <v>32.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Dinamo Makhachkala</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
@@ -2098,7 +2110,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Russia Premier League</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2115,16 +2127,16 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>30</v>
       </c>
       <c r="S15" t="n">
-        <v>26.9</v>
+        <v>30.4</v>
       </c>
       <c r="T15" t="n">
-        <v>45.6</v>
+        <v>39.6</v>
       </c>
       <c r="U15" t="n">
-        <v>41.79</v>
+        <v>21.57</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2143,23 +2155,23 @@
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>51.5</v>
+        <v>55.6</v>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="n">
-        <v>28.8</v>
+        <v>32.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>30.8</v>
+        <v>33.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>40.4</v>
+        <v>34</v>
       </c>
       <c r="AE15" t="n">
-        <v>51.5</v>
+        <v>55.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>30.4</v>
+        <v>32</v>
       </c>
       <c r="AG15" t="n">
         <v>60</v>
@@ -2168,27 +2180,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Bucaramanga</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Independiente Medellin</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -2205,11 +2217,11 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Russia Premier League</t>
+          <t>Colombia Primera A</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2219,23 +2231,23 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>26</v>
+        <v>39.5</v>
       </c>
       <c r="S16" t="n">
-        <v>28.9</v>
+        <v>35.1</v>
       </c>
       <c r="T16" t="n">
-        <v>45.1</v>
+        <v>25.4</v>
       </c>
       <c r="U16" t="n">
-        <v>14.35</v>
+        <v>20.25</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2254,52 +2266,52 @@
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>57.5</v>
+        <v>40.2</v>
       </c>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="n">
-        <v>31.9</v>
+        <v>34.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>32.1</v>
+        <v>44.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>36</v>
+        <v>21.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>57.5</v>
+        <v>40.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>30.7</v>
+        <v>21.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rot-Weiß Essen</t>
+          <t>Akhmat</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -2320,7 +2332,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Premier League</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2337,16 +2349,16 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="S17" t="n">
-        <v>24.4</v>
+        <v>30.2</v>
       </c>
       <c r="T17" t="n">
-        <v>45</v>
+        <v>38.9</v>
       </c>
       <c r="U17" t="n">
-        <v>27.07</v>
+        <v>22.42</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2365,23 +2377,23 @@
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>54.1</v>
+        <v>55.4</v>
       </c>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="n">
-        <v>28.6</v>
+        <v>32.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>22.6</v>
+        <v>34.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>48.8</v>
+        <v>33.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>54.1</v>
+        <v>55.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>28.4</v>
+        <v>32.2</v>
       </c>
       <c r="AG17" t="n">
         <v>60</v>
@@ -2395,22 +2407,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Red Bull Salzburg</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
@@ -2427,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2448,16 +2460,16 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>27.9</v>
+        <v>34.6</v>
       </c>
       <c r="S18" t="n">
-        <v>27.6</v>
+        <v>26.5</v>
       </c>
       <c r="T18" t="n">
-        <v>44.5</v>
+        <v>38.9</v>
       </c>
       <c r="U18" t="n">
-        <v>43.3</v>
+        <v>10.54</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2476,52 +2488,52 @@
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>56.5</v>
+        <v>50.6</v>
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="n">
-        <v>33.1</v>
+        <v>40.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="AD18" t="n">
-        <v>40.4</v>
+        <v>34</v>
       </c>
       <c r="AE18" t="n">
-        <v>56.5</v>
+        <v>50.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>32.6</v>
+        <v>26.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FC Ingolstadt 04</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>3.6</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
@@ -2538,11 +2550,11 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>World UEFA Europa League</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2552,23 +2564,23 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>44.2</v>
+        <v>35</v>
       </c>
       <c r="S19" t="n">
-        <v>24.5</v>
+        <v>26.3</v>
       </c>
       <c r="T19" t="n">
-        <v>31.3</v>
+        <v>38.7</v>
       </c>
       <c r="U19" t="n">
-        <v>27.13</v>
+        <v>10.39</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2587,52 +2599,52 @@
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>55.4</v>
+        <v>50.8</v>
       </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="n">
-        <v>36.5</v>
+        <v>40.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>24.2</v>
+        <v>25.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>39.3</v>
+        <v>33.9</v>
       </c>
       <c r="AE19" t="n">
-        <v>55.4</v>
+        <v>50.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>27.4</v>
+        <v>26.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FC Saarbrücken</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="E20" t="n">
         <v>3.4</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
@@ -2653,7 +2665,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>England League One</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2670,16 +2682,16 @@
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>31.5</v>
+        <v>31.8</v>
       </c>
       <c r="S20" t="n">
-        <v>25.3</v>
+        <v>29.7</v>
       </c>
       <c r="T20" t="n">
-        <v>43.2</v>
+        <v>38.5</v>
       </c>
       <c r="U20" t="n">
-        <v>28.53</v>
+        <v>39.14</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2698,23 +2710,23 @@
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>54</v>
+        <v>55.8</v>
       </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>22.8</v>
+        <v>33.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>48.6</v>
+        <v>35.9</v>
       </c>
       <c r="AE20" t="n">
-        <v>54</v>
+        <v>55.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>28.3</v>
+        <v>31.3</v>
       </c>
       <c r="AG20" t="n">
         <v>60</v>
@@ -2728,22 +2740,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Anderlecht</t>
+          <t>Plzen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Union St. Gilloise</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="E21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
@@ -2760,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2781,16 +2793,16 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>30.4</v>
+        <v>37.5</v>
       </c>
       <c r="S21" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="T21" t="n">
-        <v>43.1</v>
+        <v>36.1</v>
       </c>
       <c r="U21" t="n">
-        <v>44.12</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2809,49 +2821,49 @@
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>60.3</v>
+        <v>52.1</v>
       </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="n">
-        <v>27.7</v>
+        <v>41.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>26.8</v>
+        <v>24.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>45.5</v>
+        <v>33.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>60.3</v>
+        <v>52.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>29.2</v>
+        <v>26.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>FC Rostov</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SV Wehen</t>
+          <t>Dynamo</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="F22" t="n">
         <v>2.4</v>
@@ -2875,7 +2887,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Premier League</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2892,16 +2904,16 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>32.6</v>
+        <v>32.2</v>
       </c>
       <c r="S22" t="n">
-        <v>26.1</v>
+        <v>30.5</v>
       </c>
       <c r="T22" t="n">
-        <v>41.3</v>
+        <v>37.3</v>
       </c>
       <c r="U22" t="n">
-        <v>29.09</v>
+        <v>23.66</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2920,701 +2932,25 @@
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>54</v>
+        <v>54.9</v>
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="n">
-        <v>28.9</v>
+        <v>33.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>22.9</v>
+        <v>34.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>48.2</v>
+        <v>31.9</v>
       </c>
       <c r="AE22" t="n">
-        <v>54</v>
+        <v>54.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>28.1</v>
+        <v>32.6</v>
       </c>
       <c r="AG22" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Once Caldas</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Deportes Tolima</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>48</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Colombia Primera A</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>⏭</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
-        <v>41</v>
-      </c>
-      <c r="S23" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="U23" t="n">
-        <v>21.01</v>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Levante</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>60</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>⏭</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="S24" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>LDU de Quito</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>24</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Libertadores</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>⏭</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="T25" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="U25" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>47</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Deportivo La Coruna</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>60</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>⏭</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="T26" t="n">
-        <v>31</v>
-      </c>
-      <c r="U26" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>FK Yenisey</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Arsenal Tula</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>60</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Russia First League</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>⏭</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>33</v>
-      </c>
-      <c r="P27" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>25</v>
-      </c>
-      <c r="R27" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y27" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Rodina Moskva</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Rubin</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>60</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Russia Premier League</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>⏭</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="T28" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>33</v>
-      </c>
-      <c r="AG28" t="n">
         <v>60</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG22"/>
+  <dimension ref="A1:AG43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,27 +586,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>PFC Sochi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>SKA-Khabarovsk</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1.4</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="F2" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -624,14 +624,14 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>68.7</v>
       </c>
       <c r="K2" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Russia First League</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -644,29 +644,35 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="R2" t="n">
-        <v>62.2</v>
+        <v>63.1</v>
       </c>
       <c r="S2" t="n">
-        <v>19.7</v>
+        <v>21.6</v>
       </c>
       <c r="T2" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="U2" t="n">
-        <v>8.52</v>
+        <v>8.81</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -674,54 +680,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>57.7</v>
+      </c>
       <c r="Z2" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>35.3</v>
+      </c>
       <c r="AB2" t="n">
-        <v>49.8</v>
+        <v>44.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.7</v>
+        <v>28.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>28.5</v>
+        <v>27.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="AF2" t="n">
-        <v>27.7</v>
+        <v>32.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -730,28 +740,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2개 이상 모델 합의</t>
+          <t>모든 모델 합의</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -763,16 +773,16 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>69.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="S3" t="n">
-        <v>16.1</v>
+        <v>20.7</v>
       </c>
       <c r="T3" t="n">
-        <v>14.8</v>
+        <v>17.2</v>
       </c>
       <c r="U3" t="n">
-        <v>6.11</v>
+        <v>12.58</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -791,52 +801,52 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>51.7</v>
+        <v>56.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.5</v>
+        <v>18.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>27.8</v>
+        <v>24.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
         <v>29.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nizhny Novgorod</t>
+          <t>Sarpsborg 08 FF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="F4" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -857,11 +867,11 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Russia First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -878,16 +888,16 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>58.4</v>
+        <v>58.6</v>
       </c>
       <c r="S4" t="n">
-        <v>23.5</v>
+        <v>21.3</v>
       </c>
       <c r="T4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="U4" t="n">
-        <v>12.19</v>
+        <v>15.78</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -906,52 +916,52 @@
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>49.4</v>
+        <v>58.6</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>44.6</v>
+        <v>59.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>27.9</v>
+        <v>18.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>27.5</v>
+        <v>21.8</v>
       </c>
       <c r="AE4" t="n">
-        <v>49.4</v>
+        <v>58.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>30.6</v>
+        <v>32.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lillestrom</t>
+          <t>Waalwijk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
         <v>4.6</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -972,11 +982,11 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -993,16 +1003,16 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>57.6</v>
+        <v>56.7</v>
       </c>
       <c r="S5" t="n">
-        <v>21.1</v>
+        <v>19.8</v>
       </c>
       <c r="T5" t="n">
-        <v>21.3</v>
+        <v>23.6</v>
       </c>
       <c r="U5" t="n">
-        <v>8.699999999999999</v>
+        <v>15.02</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1021,52 +1031,52 @@
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>50</v>
+        <v>62.6</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>48.4</v>
+        <v>55.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.7</v>
+        <v>14.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>50</v>
+        <v>62.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>26.8</v>
+        <v>36.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="F6" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1087,11 +1097,11 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Russia First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1108,16 +1118,16 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>54.1</v>
+        <v>55.2</v>
       </c>
       <c r="S6" t="n">
-        <v>26.3</v>
+        <v>19.6</v>
       </c>
       <c r="T6" t="n">
-        <v>19.6</v>
+        <v>25.3</v>
       </c>
       <c r="U6" t="n">
-        <v>16.23</v>
+        <v>16.66</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1136,99 +1146,103 @@
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>49.4</v>
+        <v>63.1</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>42.2</v>
+        <v>55</v>
       </c>
       <c r="AC6" t="n">
-        <v>29.7</v>
+        <v>14.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>28.1</v>
+        <v>30.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>49.4</v>
+        <v>63.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AG6" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Águilas Doradas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1899 Hoffenheim</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8.1</v>
+        <v>1.3</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
+          <t>최소 기준 통과</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Colombia Primera A</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⏭</t>
+          <t>★</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>21.8</v>
+        <v>55</v>
       </c>
       <c r="S7" t="n">
-        <v>19.9</v>
+        <v>29.6</v>
       </c>
       <c r="T7" t="n">
-        <v>58.3</v>
+        <v>15.4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.92</v>
+        <v>13.58</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1247,173 +1261,167 @@
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>53.4</v>
+        <v>50</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
-        <v>39.2</v>
+        <v>31</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.6</v>
+        <v>46.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>39.2</v>
+        <v>22.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>53.4</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>32.5</v>
+        <v>24.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FK Orenburg</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FK Krasnodar</t>
+          <t>Standard Liege</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
+          <t>최소 기준 통과</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Russia Premier League</t>
+          <t>Belgium Jupiler Pro League</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⏭</t>
+          <t>★</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>11</v>
-      </c>
-      <c r="P8" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q8" t="n">
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>56</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="AG8" t="n">
         <v>58</v>
-      </c>
-      <c r="R8" t="n">
-        <v>19</v>
-      </c>
-      <c r="S8" t="n">
-        <v>29</v>
-      </c>
-      <c r="T8" t="n">
-        <v>52</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ferencvarosi TC</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>17.5</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5</v>
+        <v>31</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -1430,11 +1438,11 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1451,16 +1459,16 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>52</v>
+        <v>80.7</v>
       </c>
       <c r="S9" t="n">
-        <v>22.6</v>
+        <v>8.4</v>
       </c>
       <c r="T9" t="n">
-        <v>25.4</v>
+        <v>10.9</v>
       </c>
       <c r="U9" t="n">
-        <v>7.36</v>
+        <v>2.99</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1479,52 +1487,52 @@
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>46.9</v>
+        <v>62.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.9</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>32.3</v>
+        <v>24.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>26.3</v>
+        <v>35.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>VfL Wolfsburg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>SV Darmstadt 98</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -1541,11 +1549,11 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1562,16 +1570,16 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>51</v>
+        <v>52.4</v>
       </c>
       <c r="S10" t="n">
-        <v>22.4</v>
+        <v>20.2</v>
       </c>
       <c r="T10" t="n">
-        <v>26.6</v>
+        <v>27.4</v>
       </c>
       <c r="U10" t="n">
-        <v>7.04</v>
+        <v>14.41</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1590,52 +1598,52 @@
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>50.3</v>
+        <v>58.5</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>46.5</v>
+        <v>39.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.8</v>
+        <v>17.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>32.7</v>
+        <v>42.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>50.3</v>
+        <v>58.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>26.3</v>
+        <v>27.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FK Neftekhimik</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="E11" t="n">
         <v>3.9</v>
       </c>
       <c r="F11" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1656,7 +1664,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia First League</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1666,23 +1674,23 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>50.4</v>
+        <v>25.4</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="T11" t="n">
-        <v>23.5</v>
+        <v>52.1</v>
       </c>
       <c r="U11" t="n">
-        <v>20.89</v>
+        <v>16.93</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1701,23 +1709,23 @@
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>52.1</v>
+        <v>53.5</v>
       </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="n">
-        <v>37.8</v>
+        <v>32</v>
       </c>
       <c r="AC11" t="n">
-        <v>27.5</v>
+        <v>20.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>34.7</v>
+        <v>47.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>52.1</v>
+        <v>53.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>28.8</v>
+        <v>32</v>
       </c>
       <c r="AG11" t="n">
         <v>60</v>
@@ -1726,27 +1734,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FC Orenburg</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FC Krasnodar</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="E12" t="n">
         <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -1763,11 +1771,11 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Russia Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1777,23 +1785,23 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>24.1</v>
+        <v>48.4</v>
       </c>
       <c r="S12" t="n">
-        <v>27.5</v>
+        <v>25.2</v>
       </c>
       <c r="T12" t="n">
-        <v>48.4</v>
+        <v>26.4</v>
       </c>
       <c r="U12" t="n">
-        <v>12.86</v>
+        <v>13.93</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1812,52 +1820,52 @@
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>58.5</v>
+        <v>64.3</v>
       </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="n">
-        <v>29.9</v>
+        <v>32.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>33.2</v>
+        <v>29.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>37</v>
+        <v>38.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>58.5</v>
+        <v>64.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>32.9</v>
+        <v>44.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tekstilshchik Iv.</t>
+          <t>New York City FC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>New York Red Bulls</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
@@ -1878,7 +1886,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Russia First League</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1888,38 +1896,32 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="P13" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>43.6</v>
-      </c>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>26.7</v>
+        <v>48.3</v>
       </c>
       <c r="S13" t="n">
-        <v>27.1</v>
+        <v>25.3</v>
       </c>
       <c r="T13" t="n">
-        <v>46.2</v>
+        <v>26.4</v>
       </c>
       <c r="U13" t="n">
-        <v>15.06</v>
+        <v>46.73</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1927,29 +1929,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y13" t="n">
-        <v>57.7</v>
-      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>35.3</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="n">
-        <v>35.5</v>
+        <v>40.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.3</v>
+        <v>29</v>
       </c>
       <c r="AD13" t="n">
-        <v>42.1</v>
+        <v>30.8</v>
       </c>
       <c r="AE13" t="n">
-        <v>53.8</v>
+        <v>58</v>
       </c>
       <c r="AF13" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="AG13" t="n">
         <v>60</v>
@@ -1958,27 +1956,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E14" t="n">
         <v>3.6</v>
       </c>
-      <c r="E14" t="n">
-        <v>3.8</v>
-      </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
@@ -1999,7 +1997,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2009,23 +2007,23 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>29.8</v>
+        <v>47.7</v>
       </c>
       <c r="S14" t="n">
-        <v>26.3</v>
+        <v>27.6</v>
       </c>
       <c r="T14" t="n">
-        <v>43.9</v>
+        <v>24.6</v>
       </c>
       <c r="U14" t="n">
-        <v>14.5</v>
+        <v>39.66</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2044,23 +2042,23 @@
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>53.6</v>
+        <v>57.7</v>
       </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="n">
-        <v>35.8</v>
+        <v>42.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>28.3</v>
+        <v>30.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>35.9</v>
+        <v>26.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>53.6</v>
+        <v>57.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="AG14" t="n">
         <v>60</v>
@@ -2069,27 +2067,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:45</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dinamo Makhachkala</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
@@ -2110,7 +2108,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Russia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2120,23 +2118,23 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>30</v>
+        <v>47.2</v>
       </c>
       <c r="S15" t="n">
-        <v>30.4</v>
+        <v>27.3</v>
       </c>
       <c r="T15" t="n">
-        <v>39.6</v>
+        <v>25.5</v>
       </c>
       <c r="U15" t="n">
-        <v>21.57</v>
+        <v>30.01</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2155,23 +2153,23 @@
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>55.6</v>
+        <v>48</v>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="n">
-        <v>32.2</v>
+        <v>40.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>33.9</v>
+        <v>28</v>
       </c>
       <c r="AD15" t="n">
-        <v>34</v>
+        <v>31.9</v>
       </c>
       <c r="AE15" t="n">
-        <v>55.6</v>
+        <v>48</v>
       </c>
       <c r="AF15" t="n">
-        <v>32</v>
+        <v>24.6</v>
       </c>
       <c r="AG15" t="n">
         <v>60</v>
@@ -2180,27 +2178,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Independiente Medellin</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -2217,11 +2215,11 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Colombia Primera A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2238,16 +2236,16 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>39.5</v>
+        <v>46.9</v>
       </c>
       <c r="S16" t="n">
-        <v>35.1</v>
+        <v>30.4</v>
       </c>
       <c r="T16" t="n">
-        <v>25.4</v>
+        <v>22.7</v>
       </c>
       <c r="U16" t="n">
-        <v>20.25</v>
+        <v>17.23</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2266,52 +2264,52 @@
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>40.2</v>
+        <v>48.9</v>
       </c>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="n">
-        <v>34.1</v>
+        <v>38.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>44.6</v>
+        <v>38.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>40.2</v>
+        <v>48.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>21.6</v>
+        <v>31.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>SpVgg Greuther Fürth</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Akhmat</t>
+          <t>1. FC Magdeburg</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -2328,11 +2326,11 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Russia Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2349,16 +2347,16 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S17" t="n">
-        <v>30.2</v>
+        <v>21</v>
       </c>
       <c r="T17" t="n">
-        <v>38.9</v>
+        <v>46</v>
       </c>
       <c r="U17" t="n">
-        <v>22.42</v>
+        <v>22.84</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2377,52 +2375,52 @@
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>55.4</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="n">
-        <v>32.7</v>
+        <v>34.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>34.1</v>
+        <v>13.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>33.2</v>
+        <v>52.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>55.4</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AF17" t="n">
-        <v>32.2</v>
+        <v>42.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Shinnik Yaroslavl</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Red Bull Salzburg</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
@@ -2439,11 +2437,11 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>Russia First League</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2453,23 +2451,23 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>34.6</v>
+        <v>45.6</v>
       </c>
       <c r="S18" t="n">
-        <v>26.5</v>
+        <v>29.4</v>
       </c>
       <c r="T18" t="n">
-        <v>38.9</v>
+        <v>25</v>
       </c>
       <c r="U18" t="n">
-        <v>10.54</v>
+        <v>28.48</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2488,52 +2486,52 @@
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="n">
-        <v>40.1</v>
+        <v>40.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AD18" t="n">
-        <v>34</v>
+        <v>28.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="AF18" t="n">
-        <v>26.3</v>
+        <v>28.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Hangzhou Greentown</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
@@ -2550,11 +2548,11 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>World UEFA Europa League</t>
+          <t>China Super League</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2564,23 +2562,23 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>35</v>
+        <v>44.8</v>
       </c>
       <c r="S19" t="n">
-        <v>26.3</v>
+        <v>27.5</v>
       </c>
       <c r="T19" t="n">
-        <v>38.7</v>
+        <v>27.6</v>
       </c>
       <c r="U19" t="n">
-        <v>10.39</v>
+        <v>30.79</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2599,52 +2597,52 @@
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>50.8</v>
+        <v>52.4</v>
       </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>25.9</v>
+        <v>35.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>33.9</v>
+        <v>25.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>50.8</v>
+        <v>52.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>26.4</v>
+        <v>33.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>FC UFA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
@@ -2665,7 +2663,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>England League One</t>
+          <t>Russia First League</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2675,23 +2673,23 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>31.8</v>
+        <v>43.9</v>
       </c>
       <c r="S20" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="T20" t="n">
-        <v>38.5</v>
+        <v>26.9</v>
       </c>
       <c r="U20" t="n">
-        <v>39.14</v>
+        <v>31.05</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2710,23 +2708,23 @@
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>55.8</v>
+        <v>51.6</v>
       </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC20" t="n">
         <v>30.3</v>
       </c>
-      <c r="AC20" t="n">
-        <v>33.8</v>
-      </c>
       <c r="AD20" t="n">
-        <v>35.9</v>
+        <v>28.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>55.8</v>
+        <v>51.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>31.3</v>
+        <v>28.5</v>
       </c>
       <c r="AG20" t="n">
         <v>60</v>
@@ -2735,27 +2733,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Plzen</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Union St. Gilloise</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="E21" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
@@ -2772,46 +2770,52 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>60</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Russia First League</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>24</v>
+      </c>
+      <c r="P21" t="n">
         <v>27</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>World UEFA Europa League</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>⏭</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>49</v>
+      </c>
       <c r="R21" t="n">
-        <v>37.5</v>
+        <v>29.2</v>
       </c>
       <c r="S21" t="n">
-        <v>26.4</v>
+        <v>27.2</v>
       </c>
       <c r="T21" t="n">
-        <v>36.1</v>
+        <v>43.6</v>
       </c>
       <c r="U21" t="n">
-        <v>9.119999999999999</v>
+        <v>20.77</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2819,54 +2823,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>32.3</v>
+      </c>
       <c r="Z21" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="AA21" t="inlineStr"/>
+        <v>51.7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>14.3</v>
+      </c>
       <c r="AB21" t="n">
-        <v>41.6</v>
+        <v>36.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>24.9</v>
+        <v>22.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>33.6</v>
+        <v>40.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>26.7</v>
+        <v>27.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FC Rostov</t>
+          <t>Jong Ajax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dynamo</t>
+          <t>Roda</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="E22" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
@@ -2883,11 +2891,11 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Russia Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2904,16 +2912,16 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>32.2</v>
+        <v>33.9</v>
       </c>
       <c r="S22" t="n">
-        <v>30.5</v>
+        <v>23.5</v>
       </c>
       <c r="T22" t="n">
-        <v>37.3</v>
+        <v>42.6</v>
       </c>
       <c r="U22" t="n">
-        <v>23.66</v>
+        <v>14.49</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2932,26 +2940,2367 @@
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>54.9</v>
+        <v>59</v>
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="n">
-        <v>33.6</v>
+        <v>45.2</v>
       </c>
       <c r="AC22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>59</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jong Utrecht</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VVV Venlo</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>41</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FC Eindhoven</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Emmen</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>41</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>40</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Heracles</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>41</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="S26" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="U26" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Verl</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Würzburger Kickers</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>60</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="S27" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T27" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FC OSS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dordrecht</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>41</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="S28" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="T28" t="n">
         <v>34.5</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="U28" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="n">
+        <v>49</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>55</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="S29" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>52</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="S30" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sochaux</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>40</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="n">
+        <v>40</v>
+      </c>
+      <c r="S31" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="U31" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="n">
+        <v>37</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PAU</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>40</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="S32" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>40</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="S33" t="n">
+        <v>28</v>
+      </c>
+      <c r="T33" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="n">
+        <v>37</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>43</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="S34" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="U34" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AF34" t="n">
         <v>31.9</v>
       </c>
-      <c r="AE22" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="AG22" t="n">
+      <c r="AG34" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Clermont Foot</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>40</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>28</v>
+      </c>
+      <c r="U35" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>40</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="U36" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jong AZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>41</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="S37" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kasımpaşa</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Konyaspor</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>43</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>36</v>
+      </c>
+      <c r="U38" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ceara</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>44</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="S39" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>38</v>
+      </c>
+      <c r="U39" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Central Cordoba de Santiago</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Defensa Y Justicia</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>60</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Argentina Liga Profesional</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="S40" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="U40" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Queen's Park</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ayr Utd</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>27</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Scotland Championship</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="S41" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T41" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FK Chelyabinsk</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FK Ufa</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>60</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Russia First League</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>17</v>
+      </c>
+      <c r="P42" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>47</v>
+      </c>
+      <c r="R42" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="S42" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="U42" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>56</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="S43" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="U43" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,27 +586,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Independiente Medellin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Operario-PR</t>
+          <t>Jaguares</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -615,28 +615,28 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>최소 기준 통과</t>
+          <t>2개 이상 모델 합의</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Colombia Primera A</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -648,16 +648,16 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>54.3</v>
+        <v>57.1</v>
       </c>
       <c r="S2" t="n">
-        <v>24.6</v>
+        <v>28.4</v>
       </c>
       <c r="T2" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="U2" t="n">
-        <v>21.77</v>
+        <v>12.44</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -676,359 +676,26 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>56.7</v>
+        <v>51.7</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>53.4</v>
+        <v>32</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.3</v>
+        <v>46</v>
       </c>
       <c r="AD2" t="n">
-        <v>26.3</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>56.7</v>
+        <v>51.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>21.3</v>
+        <v>27.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Central Espanol</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Atletico Torque</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>43</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Uruguay Primera División</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>⏭</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
-        <v>30</v>
-      </c>
-      <c r="S3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Barracas Central</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Independ. Rivadavia</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>60</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Argentina Liga Profesional</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>⏭</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>33.94</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Aldosivi</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Atletico Tucuman</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>60</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Argentina Liga Profesional</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>⏭</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>34</v>
-      </c>
-      <c r="U5" t="n">
-        <v>36.47</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>33</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,292 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>시간</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>홈팀</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>원정팀</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>홈승배당</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>무승부배당</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>원정승배당</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>AI추천</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>신뢰도</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>판정근거</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>예상확률</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>총경기수</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>리그</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>신호등급</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>정배위치</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>FB_홈승확률</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>FB_무승부확률</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>FB_원정승확률</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>최종_홈승확률</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>최종_무승부확률</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>최종_원정승확률</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>유효표본</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>FB_예상점수</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>FB_예측결과</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>FB_평균득점</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>오버25예측</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>오버25구간실적</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>오버35예측</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>유사_홈승실적</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>유사_무실적</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>유사_원정실적</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>유사_오버25</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>유사_오버35</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>유사경기수</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Independiente Medellin</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Jaguares</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2개 이상 모델 합의</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>58</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Colombia Primera A</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="T2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>58</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,9 +413,1299 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>홈팀</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>원정팀</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>홈승배당</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>무승부배당</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>원정승배당</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>AI추천</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>신뢰도</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>판정근거</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>예상확률</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>총경기수</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>리그</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>신호등급</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>정배위치</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>FB_홈승확률</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>FB_무승부확률</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>FB_원정승확률</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>최종_홈승확률</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>최종_무승부확률</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>최종_원정승확률</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>유효표본</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>FB_예상점수</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>FB_예측결과</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>FB_평균득점</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>오버25예측</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>오버25구간실적</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>오버35예측</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>유사_홈승실적</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>유사_무실적</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>유사_원정실적</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>유사_오버25</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>유사_오버35</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>유사경기수</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inverness CT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2개 이상 모델 합의</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>32</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Scotland Championship</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2개 이상 모델 합의</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2개 이상 모델 합의</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="S4" t="n">
+        <v>23</v>
+      </c>
+      <c r="T4" t="n">
+        <v>19</v>
+      </c>
+      <c r="U4" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>60</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="S5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U5" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arbroath</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Queen's Park</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>32</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Scotland Championship</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Havelse</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fortuna Köln</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>47</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ayr Utd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Stenhousemuir</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Scotland Championship</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>42</v>
+      </c>
+      <c r="S8" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dordrecht</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>62</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Raith Rovers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Livingston</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Scotland Championship</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>31</v>
+      </c>
+      <c r="U10" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chico</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>60</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Colombia Primera A</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>30</v>
+      </c>
+      <c r="U11" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AG47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,27 +586,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Morton</t>
+          <t>FC Eindhoven</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1.3</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="F2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -615,28 +615,28 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2개 이상 모델 합의</t>
+          <t>모든 모델 합의</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -648,16 +648,16 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>60.4</v>
+        <v>66.7</v>
       </c>
       <c r="S2" t="n">
-        <v>24.6</v>
+        <v>16.1</v>
       </c>
       <c r="T2" t="n">
-        <v>15</v>
+        <v>17.2</v>
       </c>
       <c r="U2" t="n">
-        <v>7.14</v>
+        <v>8.44</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -676,52 +676,52 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>41.1</v>
+        <v>61.5</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>45.8</v>
+        <v>61.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>22.2</v>
+        <v>26.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>41.1</v>
+        <v>61.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>23.9</v>
+        <v>33.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>FC OSS</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="F3" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -730,28 +730,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2개 이상 모델 합의</t>
+          <t>모든 모델 합의</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -763,16 +763,16 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>59.4</v>
+        <v>60.9</v>
       </c>
       <c r="S3" t="n">
-        <v>21.7</v>
+        <v>17.7</v>
       </c>
       <c r="T3" t="n">
-        <v>18.8</v>
+        <v>21.3</v>
       </c>
       <c r="U3" t="n">
-        <v>17.67</v>
+        <v>14.5</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -791,52 +791,52 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>58</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>57.5</v>
+        <v>60.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.7</v>
+        <v>12.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>23.8</v>
+        <v>26.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>58</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>24.4</v>
+        <v>36.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="F4" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -857,11 +857,11 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -878,16 +878,16 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>57.9</v>
+        <v>59.2</v>
       </c>
       <c r="S4" t="n">
-        <v>23</v>
+        <v>21.8</v>
       </c>
       <c r="T4" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="U4" t="n">
-        <v>19.1</v>
+        <v>7.01</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -906,62 +906,66 @@
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>57.8</v>
+        <v>53.2</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>56.6</v>
+        <v>49.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>19.1</v>
+        <v>22.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>24.3</v>
+        <v>28.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>57.8</v>
+        <v>53.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>23.2</v>
+        <v>31</v>
       </c>
       <c r="AG4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Orlando City SC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="F5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>5.9</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
+          <t>2개 이상 모델 합의</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -972,12 +976,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA Major League Soccer</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⏭</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -989,16 +993,16 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>52.9</v>
+        <v>56.7</v>
       </c>
       <c r="S5" t="n">
-        <v>24.2</v>
+        <v>20.7</v>
       </c>
       <c r="T5" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="U5" t="n">
-        <v>20.02</v>
+        <v>37.08</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1017,23 +1021,23 @@
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>45.7</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>36.9</v>
+        <v>40.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>29</v>
+        <v>25.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>34.1</v>
+        <v>34.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>45.7</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>22.3</v>
+        <v>32.3</v>
       </c>
       <c r="AG5" t="n">
         <v>60</v>
@@ -1042,53 +1046,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
+          <t>2개 이상 모델 합의</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England League Two</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⏭</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1096,29 +1104,35 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>56</v>
+      </c>
+      <c r="P6" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>15</v>
+      </c>
       <c r="R6" t="n">
-        <v>49.8</v>
+        <v>56.3</v>
       </c>
       <c r="S6" t="n">
-        <v>29.8</v>
+        <v>27.5</v>
       </c>
       <c r="T6" t="n">
-        <v>20.4</v>
+        <v>16.2</v>
       </c>
       <c r="U6" t="n">
-        <v>15.18</v>
+        <v>24.92</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1126,110 +1140,124 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>8</v>
+      </c>
       <c r="Z6" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
+        <v>45.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.9</v>
+      </c>
       <c r="AB6" t="n">
-        <v>46.3</v>
+        <v>57</v>
       </c>
       <c r="AC6" t="n">
-        <v>33.3</v>
+        <v>31.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>20.4</v>
+        <v>11.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>37.2</v>
+        <v>45.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>22.9</v>
+        <v>23.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
+          <t>최소 기준 통과</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="K7" t="n">
         <v>60</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>England League One</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⏭</t>
+          <t>★</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>54</v>
+      </c>
+      <c r="P7" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>20</v>
+      </c>
       <c r="R7" t="n">
-        <v>30.8</v>
+        <v>56</v>
       </c>
       <c r="S7" t="n">
-        <v>25.6</v>
+        <v>24.5</v>
       </c>
       <c r="T7" t="n">
-        <v>43.6</v>
+        <v>19.5</v>
       </c>
       <c r="U7" t="n">
-        <v>33.52</v>
+        <v>11.37</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1237,25 +1265,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
+      <c r="Y7" t="n">
+        <v>76.2</v>
+      </c>
       <c r="Z7" t="n">
         <v>55.2</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
+      <c r="AA7" t="n">
+        <v>56.7</v>
+      </c>
       <c r="AB7" t="n">
-        <v>29.6</v>
+        <v>36.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>23.4</v>
+        <v>33.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>47</v>
+        <v>30.6</v>
       </c>
       <c r="AE7" t="n">
         <v>55.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>29.5</v>
+        <v>31.8</v>
       </c>
       <c r="AG7" t="n">
         <v>60</v>
@@ -1264,53 +1296,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ayr Utd</t>
+          <t>FC Volendam</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>VVV Venlo</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>3.7</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>확률·격차·표본·합의 기준 미달</t>
+          <t>최소 기준 통과</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⏭</t>
+          <t>★</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1322,16 +1358,16 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>55.7</v>
       </c>
       <c r="S8" t="n">
-        <v>30.4</v>
+        <v>18.4</v>
       </c>
       <c r="T8" t="n">
-        <v>27.6</v>
+        <v>25.8</v>
       </c>
       <c r="U8" t="n">
-        <v>15.91</v>
+        <v>19.95</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1350,52 +1386,52 @@
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>40.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="n">
-        <v>42.3</v>
+        <v>58.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>32.3</v>
+        <v>13.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>25.4</v>
+        <v>28</v>
       </c>
       <c r="AE8" t="n">
-        <v>40.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AF8" t="n">
-        <v>24.1</v>
+        <v>39.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -1412,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1426,23 +1462,23 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>37.7</v>
+        <v>51.3</v>
       </c>
       <c r="S9" t="n">
-        <v>22.9</v>
+        <v>21.2</v>
       </c>
       <c r="T9" t="n">
-        <v>39.5</v>
+        <v>27.5</v>
       </c>
       <c r="U9" t="n">
-        <v>23.31</v>
+        <v>23.38</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1461,52 +1497,52 @@
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>62</v>
+        <v>66.7</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>49.3</v>
+        <v>56.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.3</v>
+        <v>14.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>30.4</v>
+        <v>28.8</v>
       </c>
       <c r="AE9" t="n">
-        <v>62</v>
+        <v>66.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>6.7</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -1523,11 +1559,11 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England League One</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1540,29 +1576,35 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>46</v>
+      </c>
+      <c r="P10" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>28</v>
+      </c>
       <c r="R10" t="n">
-        <v>39.2</v>
+        <v>50.7</v>
       </c>
       <c r="S10" t="n">
-        <v>29.8</v>
+        <v>25.6</v>
       </c>
       <c r="T10" t="n">
-        <v>31</v>
+        <v>23.6</v>
       </c>
       <c r="U10" t="n">
-        <v>15.05</v>
+        <v>18.05</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1570,54 +1612,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
+      <c r="Y10" t="n">
+        <v>57.7</v>
+      </c>
       <c r="Z10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
+        <v>55.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>35.3</v>
+      </c>
       <c r="AB10" t="n">
-        <v>40.9</v>
+        <v>37.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>27.8</v>
+        <v>30.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>42</v>
+        <v>55.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>33.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chico</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1638,70 +1684,4276 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>11</v>
+      </c>
+      <c r="P11" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>63</v>
+      </c>
+      <c r="R11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>60</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="S12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>28.97</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Plymouth Argyle</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Burton Albion</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>60</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>England League One</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>47</v>
+      </c>
+      <c r="P13" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>23</v>
+      </c>
+      <c r="R13" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Volga Ulyanovsk</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FK Leningradets</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>60</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Russia First League</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>60</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>England League One</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="S15" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CA Progreso</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Racing Club (URU)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>44</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>46</v>
+      </c>
+      <c r="U16" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Rochdale</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>60</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>39</v>
+      </c>
+      <c r="P17" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>19</v>
+      </c>
+      <c r="R17" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>60</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="S18" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operario-PR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ceara</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>52</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>27</v>
+      </c>
+      <c r="T19" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cadiz</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>60</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rotherham</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>60</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>18</v>
+      </c>
+      <c r="R21" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Racing Montevideo</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>44</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="S22" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="U22" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Spartak Kostroma</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>FK Ural</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>60</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Russia First League</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>17</v>
+      </c>
+      <c r="P23" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>20</v>
+      </c>
+      <c r="R23" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S23" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Celta de Vigo II</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sabadell</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>60</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Roda</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Waalwijk</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>51</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bromley FC</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>60</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>England League One</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="P26" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R26" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="S26" t="n">
+        <v>35</v>
+      </c>
+      <c r="T26" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>56</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>60</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="S27" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cambridge Utd</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>60</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>England League One</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>37</v>
+      </c>
+      <c r="P28" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>31</v>
+      </c>
+      <c r="R28" t="n">
+        <v>42</v>
+      </c>
+      <c r="S28" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="T28" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Oldham</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>60</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="S29" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="T29" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Port Vale</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Northampton Town</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>60</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>34</v>
+      </c>
+      <c r="P30" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>17</v>
+      </c>
+      <c r="R30" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="S30" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New York City FC</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>60</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nautico Recife</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>52</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="S32" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="U32" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>York City</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>60</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>19</v>
+      </c>
+      <c r="P33" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>26</v>
+      </c>
+      <c r="R33" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="S33" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="T33" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="U33" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Shrewsbury</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Colchester Utd</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>60</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>37</v>
+      </c>
+      <c r="P34" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>24</v>
+      </c>
+      <c r="R34" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="S34" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AD Ceuta</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Real Sociedad B</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>60</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>21</v>
+      </c>
+      <c r="P35" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>42</v>
+      </c>
+      <c r="R35" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atletico Goianiense</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>52</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Internacional de Bogota</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>60</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>Colombia Primera A</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>⏭</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Blackpool</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>60</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>England League One</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="O38" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>39</v>
+      </c>
+      <c r="S38" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="T38" t="n">
+        <v>30</v>
+      </c>
+      <c r="U38" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Walsall FC</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>60</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="P39" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="R39" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="S39" t="n">
+        <v>38</v>
+      </c>
+      <c r="T39" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AD Ceuta FC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>60</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>60</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>18</v>
+      </c>
+      <c r="P41" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>36</v>
+      </c>
+      <c r="R41" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="S41" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>60</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>34</v>
+      </c>
+      <c r="S42" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>37</v>
+      </c>
+      <c r="U42" t="n">
+        <v>43.03</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Wycombe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>60</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>England League One</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>21</v>
+      </c>
+      <c r="P43" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>37</v>
+      </c>
+      <c r="R43" t="n">
+        <v>28</v>
+      </c>
+      <c r="S43" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="U43" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y43" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>52</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>60</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Colombia Primera A</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="S44" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="T44" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mansfield</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Leyton Orient</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>60</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>England League One</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>26</v>
+      </c>
+      <c r="P45" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>41</v>
+      </c>
+      <c r="R45" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="T45" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y45" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>33</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>60</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>England League Two</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="P46" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="S46" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="T46" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y46" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FK Chelyabinsk</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FK Yenisey</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>확률·격차·표본·합의 기준 미달</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>60</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Russia First League</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>⏭</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>30</v>
+      </c>
+      <c r="P47" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>28</v>
+      </c>
+      <c r="R47" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="S47" t="n">
         <v>34.6</v>
       </c>
-      <c r="S11" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>30</v>
-      </c>
-      <c r="U11" t="n">
-        <v>22.02</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="T47" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="U47" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AG47" t="n">
         <v>60</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -586,27 +586,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wanderers</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Colombia Primera A</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -637,23 +637,23 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>41.8</v>
+        <v>25.2</v>
       </c>
       <c r="S2" t="n">
-        <v>26.7</v>
+        <v>29</v>
       </c>
       <c r="T2" t="n">
-        <v>31.5</v>
+        <v>45.8</v>
       </c>
       <c r="U2" t="n">
-        <v>28.37</v>
+        <v>18.99</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -672,23 +672,23 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>44.1</v>
+        <v>54.5</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>41.6</v>
+        <v>30.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.3</v>
+        <v>30.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>34.1</v>
+        <v>38.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>44.1</v>
+        <v>54.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>28</v>
+        <v>31.2</v>
       </c>
       <c r="AG2" t="n">
         <v>60</v>
